--- a/test_samples/FEMARIA/sample1_ref.xlsx
+++ b/test_samples/FEMARIA/sample1_ref.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="9825" yWindow="4965" windowWidth="26550" windowHeight="15225" tabRatio="819" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="22470" yWindow="-10830" windowWidth="17160" windowHeight="9420" tabRatio="819" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DWIHARTA" sheetId="1" state="visible" r:id="rId1"/>
@@ -489,24 +489,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <dimension ref="A1:R12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="17.375" customWidth="1" style="5" min="1" max="1"/>
-    <col width="19.5" customWidth="1" style="5" min="2" max="2"/>
-    <col width="29.5" customWidth="1" style="5" min="3" max="3"/>
+    <col width="17.36328125" customWidth="1" style="5" min="1" max="1"/>
+    <col width="19.453125" customWidth="1" style="5" min="2" max="2"/>
+    <col width="29.453125" customWidth="1" style="5" min="3" max="3"/>
     <col width="26" customWidth="1" style="5" min="4" max="4"/>
-    <col width="25.5" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
-    <col width="17.875" customWidth="1" style="5" min="6" max="6"/>
-    <col width="29.25" customWidth="1" style="5" min="7" max="7"/>
-    <col width="13.75" customWidth="1" style="5" min="8" max="9"/>
-    <col width="17.625" customWidth="1" style="5" min="10" max="10"/>
-    <col width="20" customWidth="1" style="5" min="11" max="11"/>
-    <col width="16.875" bestFit="1" customWidth="1" style="5" min="12" max="12"/>
-    <col width="18.625" bestFit="1" customWidth="1" style="5" min="13" max="13"/>
-    <col width="16.375" customWidth="1" style="5" min="14" max="14"/>
-    <col width="29" bestFit="1" customWidth="1" style="5" min="15" max="15"/>
-    <col width="15.125" bestFit="1" customWidth="1" style="5" min="16" max="16"/>
+    <col width="25.453125" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="17.90625" customWidth="1" style="5" min="6" max="7"/>
+    <col width="29.26953125" customWidth="1" style="5" min="8" max="8"/>
+    <col width="13.7265625" customWidth="1" style="5" min="9" max="10"/>
+    <col width="17.6328125" customWidth="1" style="5" min="11" max="11"/>
+    <col width="20" customWidth="1" style="5" min="12" max="12"/>
+    <col width="16.90625" bestFit="1" customWidth="1" style="5" min="13" max="13"/>
+    <col width="18.6328125" bestFit="1" customWidth="1" style="5" min="14" max="14"/>
+    <col width="16.36328125" customWidth="1" style="5" min="15" max="15"/>
+    <col width="29" bestFit="1" customWidth="1" style="5" min="16" max="16"/>
+    <col width="15.08984375" bestFit="1" customWidth="1" style="5" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customFormat="1" customHeight="1" s="1">
@@ -548,61 +548,72 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
           <t>Order No.</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Arrive Date
 到達日</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>on board date
 開船日</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>B/L NO.
 提單號碼</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>MBL NO.
 主提單號碼</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Port of Loading
 啟運港</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Port of discharge
 目的港</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Volume
 材積</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Vessel
 船名</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Container no.
 貨櫃號碼</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Shipper
+出貨方</t>
         </is>
       </c>
     </row>
@@ -633,11 +644,7 @@
       <c r="F2" s="3" t="n">
         <v>699300</v>
       </c>
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G2" s="3" t="n"/>
       <c r="H2" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -650,7 +657,7 @@
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
-          <t>KMTCSGN6098229</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K2" s="0" t="inlineStr">
@@ -660,7 +667,7 @@
       </c>
       <c r="L2" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KMTCSGN6098229</t>
         </is>
       </c>
       <c r="M2" s="0" t="inlineStr">
@@ -670,17 +677,27 @@
       </c>
       <c r="N2" s="0" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O2" s="0" t="inlineStr">
+        <is>
           <t>1x20 FT</t>
         </is>
       </c>
-      <c r="O2" s="0" t="inlineStr">
+      <c r="P2" s="0" t="inlineStr">
         <is>
           <t>INCHEON VOYAGER V.2509S</t>
         </is>
       </c>
-      <c r="P2" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="Q2" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R2" s="0" t="inlineStr">
+        <is>
+          <t>EVER BRAVE DEVELOPMENTS LIMITED</t>
         </is>
       </c>
     </row>
@@ -711,11 +728,7 @@
       <c r="F3" s="3" t="n">
         <v>2276380</v>
       </c>
-      <c r="G3" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G3" s="3" t="n"/>
       <c r="H3" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -728,7 +741,7 @@
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>KMTCSGN6098229</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K3" s="0" t="inlineStr">
@@ -738,7 +751,7 @@
       </c>
       <c r="L3" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KMTCSGN6098229</t>
         </is>
       </c>
       <c r="M3" s="0" t="inlineStr">
@@ -748,17 +761,27 @@
       </c>
       <c r="N3" s="0" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" s="0" t="inlineStr">
+        <is>
           <t>1x20 FT</t>
         </is>
       </c>
-      <c r="O3" s="0" t="inlineStr">
+      <c r="P3" s="0" t="inlineStr">
         <is>
           <t>INCHEON VOYAGER V.2509S</t>
         </is>
       </c>
-      <c r="P3" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="Q3" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R3" s="0" t="inlineStr">
+        <is>
+          <t>EVER BRAVE DEVELOPMENTS LIMITED</t>
         </is>
       </c>
     </row>
@@ -789,11 +812,7 @@
       <c r="F4" s="3" t="n">
         <v>1135530</v>
       </c>
-      <c r="G4" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G4" s="3" t="n"/>
       <c r="H4" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -806,7 +825,7 @@
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t>KMTCSGN6098229</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
@@ -816,7 +835,7 @@
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KMTCSGN6098229</t>
         </is>
       </c>
       <c r="M4" s="0" t="inlineStr">
@@ -826,17 +845,27 @@
       </c>
       <c r="N4" s="0" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" s="0" t="inlineStr">
+        <is>
           <t>1x20 FT</t>
         </is>
       </c>
-      <c r="O4" s="0" t="inlineStr">
+      <c r="P4" s="0" t="inlineStr">
         <is>
           <t>INCHEON VOYAGER V.2509S</t>
         </is>
       </c>
-      <c r="P4" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="Q4" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R4" s="0" t="inlineStr">
+        <is>
+          <t>EVER BRAVE DEVELOPMENTS LIMITED</t>
         </is>
       </c>
     </row>
@@ -867,11 +896,7 @@
       <c r="F5" s="3" t="n">
         <v>25000</v>
       </c>
-      <c r="G5" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G5" s="3" t="n"/>
       <c r="H5" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -884,7 +909,7 @@
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t>KMTCSGN6098229</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
@@ -894,7 +919,7 @@
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KMTCSGN6098229</t>
         </is>
       </c>
       <c r="M5" s="0" t="inlineStr">
@@ -904,17 +929,27 @@
       </c>
       <c r="N5" s="0" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="0" t="inlineStr">
+        <is>
           <t>1x20 FT</t>
         </is>
       </c>
-      <c r="O5" s="0" t="inlineStr">
+      <c r="P5" s="0" t="inlineStr">
         <is>
           <t>INCHEON VOYAGER V.2509S</t>
         </is>
       </c>
-      <c r="P5" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="Q5" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="0" t="inlineStr">
+        <is>
+          <t>EVER BRAVE DEVELOPMENTS LIMITED</t>
         </is>
       </c>
     </row>
@@ -945,11 +980,7 @@
       <c r="F6" s="3" t="n">
         <v>300000</v>
       </c>
-      <c r="G6" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G6" s="3" t="n"/>
       <c r="H6" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -962,7 +993,7 @@
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t>KMTCSGN6098229</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K6" s="0" t="inlineStr">
@@ -972,7 +1003,7 @@
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KMTCSGN6098229</t>
         </is>
       </c>
       <c r="M6" s="0" t="inlineStr">
@@ -982,17 +1013,27 @@
       </c>
       <c r="N6" s="0" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="0" t="inlineStr">
+        <is>
           <t>1x20 FT</t>
         </is>
       </c>
-      <c r="O6" s="0" t="inlineStr">
+      <c r="P6" s="0" t="inlineStr">
         <is>
           <t>INCHEON VOYAGER V.2509S</t>
         </is>
       </c>
-      <c r="P6" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="Q6" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="0" t="inlineStr">
+        <is>
+          <t>EVER BRAVE DEVELOPMENTS LIMITED</t>
         </is>
       </c>
     </row>
@@ -1023,11 +1064,7 @@
       <c r="F7" s="3" t="n">
         <v>2940000</v>
       </c>
-      <c r="G7" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="n"/>
       <c r="H7" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1040,7 +1077,7 @@
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t>KMTCSGN6098229</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K7" s="0" t="inlineStr">
@@ -1050,7 +1087,7 @@
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KMTCSGN6098229</t>
         </is>
       </c>
       <c r="M7" s="0" t="inlineStr">
@@ -1060,17 +1097,27 @@
       </c>
       <c r="N7" s="0" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="0" t="inlineStr">
+        <is>
           <t>1x20 FT</t>
         </is>
       </c>
-      <c r="O7" s="0" t="inlineStr">
+      <c r="P7" s="0" t="inlineStr">
         <is>
           <t>INCHEON VOYAGER V.2509S</t>
         </is>
       </c>
-      <c r="P7" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="Q7" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="0" t="inlineStr">
+        <is>
+          <t>EVER BRAVE DEVELOPMENTS LIMITED</t>
         </is>
       </c>
     </row>
@@ -1101,11 +1148,7 @@
       <c r="F8" s="3" t="n">
         <v>123336</v>
       </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G8" s="3" t="n"/>
       <c r="H8" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1118,7 +1161,7 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t>KMTCSGN6098229</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K8" s="0" t="inlineStr">
@@ -1128,7 +1171,7 @@
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KMTCSGN6098229</t>
         </is>
       </c>
       <c r="M8" s="0" t="inlineStr">
@@ -1138,17 +1181,27 @@
       </c>
       <c r="N8" s="0" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="0" t="inlineStr">
+        <is>
           <t>1x20 FT</t>
         </is>
       </c>
-      <c r="O8" s="0" t="inlineStr">
+      <c r="P8" s="0" t="inlineStr">
         <is>
           <t>INCHEON VOYAGER V.2509S</t>
         </is>
       </c>
-      <c r="P8" s="0" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="Q8" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="0" t="inlineStr">
+        <is>
+          <t>EVER BRAVE DEVELOPMENTS LIMITED</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1209,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="Q12" s="1" t="n"/>
+      <c r="R12" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
